--- a/2026/GENERAL PAZ 138/Abril/Abril GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Abril/Abril GRAL PAZ 138.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEC2128-30C0-4EE3-9A29-72D4BBB5C3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5419A14-12AC-4614-8714-DF01F4B87283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -287,9 +287,6 @@
     <t>EDESUR: NºCLIENTE 4139927 -  Nº Medidor 8142186</t>
   </si>
   <si>
-    <t xml:space="preserve">FED. PATRONAL - Seguro integral - Póliza Nº 1-2178160-0 / 19-31454716-0 </t>
-  </si>
-  <si>
     <t>ARNALDO</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
   </si>
   <si>
     <t>Recupero de fondo inicial puesto por administracion entrante</t>
+  </si>
+  <si>
+    <t>FED. PATRONAL - Seguro integral - Póliza Nº 2318491</t>
   </si>
 </sst>
 </file>
@@ -1554,6 +1554,54 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1562,54 +1610,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2239,7 +2239,7 @@
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="106" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="124"/>
       <c r="C32" s="91">
@@ -2270,11 +2270,11 @@
     </row>
     <row r="35" spans="1:6" ht="41.45" customHeight="1">
       <c r="A35" s="153" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B35" s="154"/>
       <c r="C35" s="93">
-        <v>83908</v>
+        <v>87914</v>
       </c>
       <c r="D35" s="88"/>
     </row>
@@ -2286,7 +2286,7 @@
       <c r="C36" s="19"/>
       <c r="D36" s="58">
         <f>SUM(C35:C35)</f>
-        <v>83908</v>
+        <v>87914</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1">
@@ -2450,10 +2450,7 @@
       </c>
       <c r="B54" s="158"/>
       <c r="C54" s="159"/>
-      <c r="D54" s="67">
-        <f>500000-310871.67</f>
-        <v>189128.33000000002</v>
-      </c>
+      <c r="D54" s="67"/>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
       <c r="A55" s="128"/>
@@ -2470,7 +2467,7 @@
       <c r="C56" s="70"/>
       <c r="D56" s="71">
         <f>(SUM(D25:D54))</f>
-        <v>500000.00000000006</v>
+        <v>314877.67000000004</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="23"/>
@@ -2570,7 +2567,7 @@
       </c>
       <c r="B70" s="143">
         <f>D56</f>
-        <v>500000.00000000006</v>
+        <v>314877.67000000004</v>
       </c>
       <c r="C70" s="144"/>
     </row>
@@ -2580,7 +2577,7 @@
       </c>
       <c r="B71" s="143">
         <f>D56-D54</f>
-        <v>310871.67000000004</v>
+        <v>314877.67000000004</v>
       </c>
       <c r="C71" s="68"/>
     </row>
@@ -2647,7 +2644,7 @@
     </row>
     <row r="80" spans="1:4" ht="14.25" customHeight="1">
       <c r="A80" s="148" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B80" s="62">
         <v>-521370</v>
@@ -2670,7 +2667,7 @@
       </c>
       <c r="B82" s="62">
         <f>-B71</f>
-        <v>-310871.67000000004</v>
+        <v>-314877.67000000004</v>
       </c>
       <c r="C82" s="68"/>
     </row>
@@ -2690,7 +2687,7 @@
       </c>
       <c r="B84" s="107">
         <f>SUM(B78:B83)</f>
-        <v>11684.890000000014</v>
+        <v>7678.890000000014</v>
       </c>
       <c r="C84" s="134"/>
     </row>
@@ -2776,19 +2773,19 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="108"/>
-      <c r="B1" s="165" t="str">
+      <c r="B1" s="161" t="str">
         <f>RESUMEN!A4</f>
         <v>TRANSFERIR A  : carolina.rc.adm - CVU: 0000003100054616492658</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
       <c r="L1" s="109"/>
       <c r="M1" s="109"/>
       <c r="N1" s="109"/>
@@ -2797,23 +2794,23 @@
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
       <c r="A2" s="111"/>
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
       <c r="L2" s="112"/>
       <c r="M2" s="112" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="119">
-        <v>500000</v>
+        <v>314877</v>
       </c>
       <c r="P2" s="113"/>
       <c r="Q2" s="9"/>
@@ -2823,16 +2820,16 @@
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
       <c r="A3" s="114"/>
-      <c r="B3" s="167"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="167"/>
-      <c r="I3" s="167"/>
-      <c r="J3" s="167"/>
-      <c r="K3" s="167"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
       <c r="L3" s="115"/>
       <c r="M3" s="115" t="s">
         <v>53</v>
@@ -2845,96 +2842,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="177" t="s">
+      <c r="B4" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="178"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="178"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="178"/>
-      <c r="O4" s="178"/>
-      <c r="P4" s="179"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="175"/>
+      <c r="K4" s="175"/>
+      <c r="L4" s="175"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="176"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="163" t="s">
+      <c r="B5" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="164" t="s">
+      <c r="C5" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="164" t="s">
+      <c r="D5" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="166" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="164" t="s">
+      <c r="F5" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="164" t="s">
+      <c r="G5" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="164" t="s">
+      <c r="H5" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="164" t="s">
+      <c r="I5" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="173" t="s">
+      <c r="J5" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="171" t="s">
+      <c r="K5" s="168" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="171" t="s">
+      <c r="L5" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="171" t="s">
+      <c r="M5" s="168" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="175" t="s">
+      <c r="N5" s="172" t="s">
         <v>48</v>
       </c>
       <c r="O5" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="168" t="s">
+      <c r="P5" s="164" t="s">
         <v>46</v>
       </c>
       <c r="S5" s="23"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="162"/>
-      <c r="B6" s="163"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="170"/>
-      <c r="J6" s="174"/>
-      <c r="K6" s="172"/>
-      <c r="L6" s="171"/>
-      <c r="M6" s="172"/>
-      <c r="N6" s="176"/>
+      <c r="A6" s="178"/>
+      <c r="B6" s="179"/>
+      <c r="C6" s="166"/>
+      <c r="D6" s="166"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="166"/>
+      <c r="G6" s="166"/>
+      <c r="H6" s="166"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="171"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="168"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="173"/>
       <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/05</v>
       </c>
-      <c r="P6" s="168"/>
+      <c r="P6" s="164"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -2957,7 +2954,7 @@
         <v>61</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="35">
@@ -2984,18 +2981,18 @@
       </c>
       <c r="M7" s="40">
         <f>O$2*F7%</f>
-        <v>55999.999999999993</v>
+        <v>35266.223999999995</v>
       </c>
       <c r="N7" s="41">
         <v>0</v>
       </c>
       <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>1208245.01</v>
+        <v>1187511.01</v>
       </c>
       <c r="P7" s="43">
         <f t="shared" ref="P7:P16" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>1244492.01</v>
+        <v>1223136.01</v>
       </c>
       <c r="Q7" s="23">
         <v>0.01</v>
@@ -3049,18 +3046,18 @@
       </c>
       <c r="M8" s="40">
         <f t="shared" ref="M8:M17" si="5">O$2*F8%</f>
-        <v>55999.999999999993</v>
+        <v>35266.223999999995</v>
       </c>
       <c r="N8" s="41">
         <v>0</v>
       </c>
       <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>836419.02</v>
+        <v>815685.02</v>
       </c>
       <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>861512.02</v>
+        <v>840156.02</v>
       </c>
       <c r="Q8" s="23">
         <f>Q7+0.01</f>
@@ -3116,18 +3113,18 @@
       </c>
       <c r="M9" s="102">
         <f t="shared" si="5"/>
-        <v>44500.000000000007</v>
+        <v>28024.053000000004</v>
       </c>
       <c r="N9" s="103">
         <v>0</v>
       </c>
       <c r="O9" s="104">
         <f t="shared" ref="O9:O16" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>40282.03</v>
+        <v>23806.03</v>
       </c>
       <c r="P9" s="105">
         <f t="shared" si="0"/>
-        <v>41490.03</v>
+        <v>24520.03</v>
       </c>
       <c r="Q9" s="23">
         <f t="shared" ref="Q9:Q16" si="7">Q8+0.01</f>
@@ -3183,18 +3180,18 @@
       </c>
       <c r="M10" s="40">
         <f t="shared" si="5"/>
-        <v>44500.000000000007</v>
+        <v>28024.053000000004</v>
       </c>
       <c r="N10" s="41">
         <v>0</v>
       </c>
       <c r="O10" s="42">
         <f t="shared" si="6"/>
-        <v>44500.04</v>
+        <v>28024.04</v>
       </c>
       <c r="P10" s="43">
         <f t="shared" si="0"/>
-        <v>45835.040000000001</v>
+        <v>28865.040000000001</v>
       </c>
       <c r="Q10" s="23">
         <f t="shared" si="7"/>
@@ -3222,7 +3219,7 @@
         <v>65</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="35">
@@ -3249,18 +3246,18 @@
       </c>
       <c r="M11" s="40">
         <f t="shared" si="5"/>
-        <v>49000</v>
+        <v>30857.946</v>
       </c>
       <c r="N11" s="41">
         <v>0</v>
       </c>
       <c r="O11" s="42">
         <f t="shared" si="6"/>
-        <v>44377.05</v>
+        <v>26235.05</v>
       </c>
       <c r="P11" s="43">
         <f t="shared" si="0"/>
-        <v>45708.05</v>
+        <v>27022.05</v>
       </c>
       <c r="Q11" s="23">
         <f t="shared" si="7"/>
@@ -3288,7 +3285,7 @@
         <v>66</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="35">
@@ -3316,18 +3313,18 @@
       </c>
       <c r="M12" s="40">
         <f t="shared" si="5"/>
-        <v>49000</v>
+        <v>30857.946</v>
       </c>
       <c r="N12" s="133">
         <v>0</v>
       </c>
       <c r="O12" s="42">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>49000.06</v>
+        <v>30858.06</v>
       </c>
       <c r="P12" s="43">
         <f t="shared" si="0"/>
-        <v>50470.06</v>
+        <v>31784.06</v>
       </c>
       <c r="Q12" s="23">
         <f t="shared" si="7"/>
@@ -3355,7 +3352,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="100">
@@ -3382,18 +3379,18 @@
       </c>
       <c r="M13" s="40">
         <f t="shared" si="5"/>
-        <v>44500.000000000007</v>
+        <v>28024.053000000004</v>
       </c>
       <c r="N13" s="41">
         <v>0</v>
       </c>
       <c r="O13" s="42">
         <f t="shared" si="6"/>
-        <v>44500.07</v>
+        <v>28024.07</v>
       </c>
       <c r="P13" s="43">
         <f t="shared" si="0"/>
-        <v>45835.07</v>
+        <v>28865.07</v>
       </c>
       <c r="Q13" s="23">
         <f t="shared" si="7"/>
@@ -3425,7 +3422,7 @@
         <v>80</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" s="100">
         <v>8.9</v>
@@ -3452,18 +3449,18 @@
       </c>
       <c r="M14" s="40">
         <f t="shared" si="5"/>
-        <v>44500.000000000007</v>
+        <v>28024.053000000004</v>
       </c>
       <c r="N14" s="41">
         <v>0</v>
       </c>
       <c r="O14" s="42">
         <f t="shared" si="6"/>
-        <v>44500.08</v>
+        <v>28024.080000000002</v>
       </c>
       <c r="P14" s="43">
         <f t="shared" si="0"/>
-        <v>45835.08</v>
+        <v>28865.08</v>
       </c>
       <c r="Q14" s="23">
         <f t="shared" si="7"/>
@@ -3494,7 +3491,7 @@
         <v>80</v>
       </c>
       <c r="E15" s="99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F15" s="35">
         <v>11.2</v>
@@ -3519,18 +3516,18 @@
       </c>
       <c r="M15" s="102">
         <f t="shared" si="5"/>
-        <v>55999.999999999993</v>
+        <v>35266.223999999995</v>
       </c>
       <c r="N15" s="103">
         <v>0</v>
       </c>
       <c r="O15" s="104">
         <f t="shared" si="6"/>
-        <v>51441.09</v>
+        <v>30707.09</v>
       </c>
       <c r="P15" s="105">
         <f t="shared" si="0"/>
-        <v>52984.09</v>
+        <v>31628.09</v>
       </c>
       <c r="Q15" s="23">
         <f t="shared" si="7"/>
@@ -3558,7 +3555,7 @@
         <v>70</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16" s="99"/>
       <c r="F16" s="35">
@@ -3585,18 +3582,18 @@
       </c>
       <c r="M16" s="40">
         <f t="shared" si="5"/>
-        <v>55999.999999999993</v>
+        <v>35266.223999999995</v>
       </c>
       <c r="N16" s="41">
         <v>0</v>
       </c>
       <c r="O16" s="42">
         <f t="shared" si="6"/>
-        <v>56000.1</v>
+        <v>35266.1</v>
       </c>
       <c r="P16" s="43">
         <f t="shared" si="0"/>
-        <v>57680.1</v>
+        <v>36324.1</v>
       </c>
       <c r="Q16" s="23">
         <f t="shared" si="7"/>
@@ -3676,7 +3673,7 @@
       </c>
       <c r="M18" s="30">
         <f>SUM(M7:M17)</f>
-        <v>500000</v>
+        <v>314877</v>
       </c>
       <c r="N18" s="30">
         <f>SUM(N7:N17)</f>
@@ -3684,11 +3681,11 @@
       </c>
       <c r="O18" s="53">
         <f>SUM(O7:O16)</f>
-        <v>2419264.5499999998</v>
+        <v>2234140.5499999998</v>
       </c>
       <c r="P18" s="53">
         <f>SUM(P7:P16)</f>
-        <v>2491841.5499999998</v>
+        <v>2301165.5499999998</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -3696,93 +3693,98 @@
       <c r="E19" s="25"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="169" t="s">
+      <c r="D21" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="169"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="169"/>
-      <c r="L21" s="169"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="169"/>
-      <c r="O21" s="169"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
+      <c r="H21" s="165"/>
+      <c r="I21" s="165"/>
+      <c r="J21" s="165"/>
+      <c r="K21" s="165"/>
+      <c r="L21" s="165"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="165"/>
+      <c r="O21" s="165"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="169"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="169"/>
-      <c r="G22" s="169"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="169"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="169"/>
-      <c r="L22" s="169"/>
-      <c r="M22" s="169"/>
-      <c r="N22" s="169"/>
-      <c r="O22" s="169"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
+      <c r="H22" s="165"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="165"/>
+      <c r="K22" s="165"/>
+      <c r="L22" s="165"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="169"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="169"/>
-      <c r="L23" s="169"/>
-      <c r="M23" s="169"/>
-      <c r="N23" s="169"/>
-      <c r="O23" s="169"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
+      <c r="H23" s="165"/>
+      <c r="I23" s="165"/>
+      <c r="J23" s="165"/>
+      <c r="K23" s="165"/>
+      <c r="L23" s="165"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="165"/>
+      <c r="O23" s="165"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="169"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="169"/>
-      <c r="G24" s="169"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="169"/>
-      <c r="J24" s="169"/>
-      <c r="K24" s="169"/>
-      <c r="L24" s="169"/>
-      <c r="M24" s="169"/>
-      <c r="N24" s="169"/>
-      <c r="O24" s="169"/>
+      <c r="D24" s="165"/>
+      <c r="E24" s="165"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="165"/>
+      <c r="H24" s="165"/>
+      <c r="I24" s="165"/>
+      <c r="J24" s="165"/>
+      <c r="K24" s="165"/>
+      <c r="L24" s="165"/>
+      <c r="M24" s="165"/>
+      <c r="N24" s="165"/>
+      <c r="O24" s="165"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="169"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="169"/>
-      <c r="G25" s="169"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="169"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="169"/>
-      <c r="L25" s="169"/>
-      <c r="M25" s="169"/>
-      <c r="N25" s="169"/>
-      <c r="O25" s="169"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="165"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="165"/>
+      <c r="H25" s="165"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="165"/>
+      <c r="K25" s="165"/>
+      <c r="L25" s="165"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="165"/>
+      <c r="O25" s="165"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="169"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="169"/>
-      <c r="G26" s="169"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="169"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="169"/>
-      <c r="L26" s="169"/>
-      <c r="M26" s="169"/>
-      <c r="N26" s="169"/>
-      <c r="O26" s="169"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="165"/>
+      <c r="H26" s="165"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="165"/>
+      <c r="K26" s="165"/>
+      <c r="L26" s="165"/>
+      <c r="M26" s="165"/>
+      <c r="N26" s="165"/>
+      <c r="O26" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3796,11 +3798,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
